--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2024.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7086,7 +7086,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8867,7 +8867,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9235,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9373,7 +9373,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9649,7 +9649,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9833,7 +9833,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9925,7 +9925,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12133,7 +12133,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12639,7 +12639,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13099,7 +13099,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13145,7 +13145,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13421,7 +13421,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13835,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14157,7 +14157,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14203,7 +14203,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14387,7 +14387,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14663,7 +14663,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -14985,7 +14985,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15353,7 +15353,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>Tasa neta básica</t>
+          <t>Tasa neta basica</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2024.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="697">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -1321,15 +1321,6 @@
     <t xml:space="preserve">Chañaral</t>
   </si>
   <si>
-    <t xml:space="preserve">Arica y Parinacota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">2301</t>
   </si>
   <si>
@@ -2071,7 +2062,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:50</t>
+    <t xml:space="preserve">2026-09-07 12:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2483,7 +2474,7 @@
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -9058,16 +9049,16 @@
         <v>2024</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C206" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D206" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D206" s="2" t="s">
+      <c r="E206" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>385</v>
@@ -9079,7 +9070,7 @@
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>92.72</v>
+        <v>92.58</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>16</v>
@@ -9096,10 +9087,10 @@
         <v>429</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>385</v>
@@ -9111,7 +9102,7 @@
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>92.58</v>
+        <v>92.34</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>16</v>
@@ -9122,10 +9113,10 @@
         <v>2024</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>439</v>
@@ -9143,7 +9134,7 @@
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>92.34</v>
+        <v>92.3</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>16</v>
@@ -9157,13 +9148,13 @@
         <v>1</v>
       </c>
       <c r="C209" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D209" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="D209" s="2" t="s">
+      <c r="E209" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>385</v>
@@ -9175,7 +9166,7 @@
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>92.3</v>
+        <v>91.88</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>16</v>
@@ -9189,13 +9180,13 @@
         <v>1</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D210" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>385</v>
@@ -9207,7 +9198,7 @@
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>91.88</v>
+        <v>91.59</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>16</v>
@@ -9221,13 +9212,13 @@
         <v>1</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D211" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>385</v>
@@ -9239,7 +9230,7 @@
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>91.59</v>
+        <v>91.3</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>16</v>
@@ -9250,16 +9241,16 @@
         <v>2024</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>385</v>
@@ -9271,7 +9262,7 @@
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>91.3</v>
+        <v>91.08</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>16</v>
@@ -9288,10 +9279,10 @@
         <v>429</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>385</v>
@@ -9303,7 +9294,7 @@
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>91.08</v>
+        <v>90.47</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>16</v>
@@ -9320,10 +9311,10 @@
         <v>429</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>385</v>
@@ -9335,7 +9326,7 @@
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>90.47</v>
+        <v>90.45</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>16</v>
@@ -9352,10 +9343,10 @@
         <v>429</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>385</v>
@@ -9367,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>90.45</v>
+        <v>90.08</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>16</v>
@@ -9378,16 +9369,16 @@
         <v>2024</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="D216" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>385</v>
@@ -9399,7 +9390,7 @@
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>90.08</v>
+        <v>89.55</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>16</v>
@@ -9413,13 +9404,13 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D217" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>385</v>
@@ -9431,7 +9422,7 @@
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>89.55</v>
+        <v>88.94</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>16</v>
@@ -9442,16 +9433,16 @@
         <v>2024</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>385</v>
@@ -9463,7 +9454,7 @@
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>88.94</v>
+        <v>86.61</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>16</v>
@@ -9474,16 +9465,16 @@
         <v>2024</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="D219" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E219" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>385</v>
@@ -9495,7 +9486,7 @@
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>86.61</v>
+        <v>79.82</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>16</v>
@@ -9506,10 +9497,10 @@
         <v>2024</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>463</v>
@@ -9518,16 +9509,16 @@
         <v>464</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>385</v>
+        <v>465</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>386</v>
+        <v>466</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>79.82</v>
+        <v>98.18</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>16</v>
@@ -9541,25 +9532,25 @@
         <v>9</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="G221" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="E221" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G221" s="2" t="s">
-        <v>469</v>
-      </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>98.18</v>
+        <v>97.9</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>16</v>
@@ -9573,25 +9564,25 @@
         <v>9</v>
       </c>
       <c r="C222" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G222" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>97.9</v>
+        <v>97.87</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>16</v>
@@ -9605,25 +9596,25 @@
         <v>9</v>
       </c>
       <c r="C223" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F223" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D223" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G223" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>97.87</v>
+        <v>97.83</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>16</v>
@@ -9634,10 +9625,10 @@
         <v>2024</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>474</v>
@@ -9646,16 +9637,16 @@
         <v>475</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>97.83</v>
+        <v>97.67</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>16</v>
@@ -9669,25 +9660,25 @@
         <v>8</v>
       </c>
       <c r="C225" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D225" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="D225" s="2" t="s">
+      <c r="E225" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="E225" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="F225" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>97.67</v>
+        <v>97.66</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>16</v>
@@ -9698,10 +9689,10 @@
         <v>2024</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>479</v>
@@ -9710,16 +9701,16 @@
         <v>480</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>97.66</v>
+        <v>97.3</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>16</v>
@@ -9730,28 +9721,28 @@
         <v>2024</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C227" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D227" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="D227" s="2" t="s">
+      <c r="E227" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="E227" s="2" t="s">
-        <v>483</v>
-      </c>
       <c r="F227" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>97.3</v>
+        <v>97.28</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>16</v>
@@ -9762,28 +9753,28 @@
         <v>2024</v>
       </c>
       <c r="B228" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D228" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G228" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>97.28</v>
+        <v>97.26</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>16</v>
@@ -9797,19 +9788,19 @@
         <v>8</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D229" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E229" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E229" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="F229" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9829,25 +9820,25 @@
         <v>8</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D230" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="E230" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="F230" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>97.26</v>
+        <v>97.19</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>16</v>
@@ -9858,28 +9849,28 @@
         <v>2024</v>
       </c>
       <c r="B231" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D231" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E231" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="E231" s="2" t="s">
-        <v>491</v>
-      </c>
       <c r="F231" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>97.19</v>
+        <v>97.17</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>16</v>
@@ -9890,28 +9881,28 @@
         <v>2024</v>
       </c>
       <c r="B232" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="D232" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E232" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="E232" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="F232" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>97.17</v>
+        <v>97.06</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>16</v>
@@ -9922,10 +9913,10 @@
         <v>2024</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>494</v>
@@ -9934,16 +9925,16 @@
         <v>495</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>97.06</v>
+        <v>96.99</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>16</v>
@@ -9954,28 +9945,28 @@
         <v>2024</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="E234" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="E234" s="2" t="s">
-        <v>498</v>
-      </c>
       <c r="F234" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>96.99</v>
+        <v>96.98</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>16</v>
@@ -9986,22 +9977,22 @@
         <v>2024</v>
       </c>
       <c r="B235" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D235" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E235" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="E235" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="F235" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -10018,28 +10009,28 @@
         <v>2024</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C236" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D236" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G236" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>96.98</v>
+        <v>96.93</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>16</v>
@@ -10050,28 +10041,28 @@
         <v>2024</v>
       </c>
       <c r="B237" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D237" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="E237" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="F237" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>96.93</v>
+        <v>96.87</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>16</v>
@@ -10082,28 +10073,28 @@
         <v>2024</v>
       </c>
       <c r="B238" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D238" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E238" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="E238" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="F238" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>96.87</v>
+        <v>96.78</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>16</v>
@@ -10114,28 +10105,28 @@
         <v>2024</v>
       </c>
       <c r="B239" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G239" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>96.78</v>
+        <v>96.74</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>16</v>
@@ -10146,28 +10137,28 @@
         <v>2024</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="D240" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E240" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="E240" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="F240" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>96.74</v>
+        <v>96.7</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>16</v>
@@ -10178,28 +10169,28 @@
         <v>2024</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D241" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="E241" s="2" t="s">
-        <v>512</v>
-      </c>
       <c r="F241" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>96.7</v>
+        <v>96.69</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>16</v>
@@ -10213,19 +10204,19 @@
         <v>8</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D242" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="E242" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="F242" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10242,22 +10233,22 @@
         <v>2024</v>
       </c>
       <c r="B243" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D243" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="E243" s="2" t="s">
-        <v>516</v>
-      </c>
       <c r="F243" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10274,22 +10265,22 @@
         <v>2024</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C244" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F244" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D244" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G244" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10306,28 +10297,28 @@
         <v>2024</v>
       </c>
       <c r="B245" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D245" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="E245" s="2" t="s">
-        <v>520</v>
-      </c>
       <c r="F245" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>96.69</v>
+        <v>96.64</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>16</v>
@@ -10338,28 +10329,28 @@
         <v>2024</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F246" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D246" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G246" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>96.64</v>
+        <v>96.61</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>16</v>
@@ -10373,19 +10364,19 @@
         <v>8</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D247" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E247" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="E247" s="2" t="s">
-        <v>524</v>
-      </c>
       <c r="F247" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10402,28 +10393,28 @@
         <v>2024</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D248" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E248" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="E248" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="F248" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>96.61</v>
+        <v>96.6</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>16</v>
@@ -10434,28 +10425,28 @@
         <v>2024</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C249" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G249" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>96.6</v>
+        <v>96.59</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>16</v>
@@ -10466,28 +10457,28 @@
         <v>2024</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D250" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E250" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="E250" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="F250" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>96.59</v>
+        <v>96.58</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>16</v>
@@ -10498,22 +10489,22 @@
         <v>2024</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F251" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D251" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G251" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10530,28 +10521,28 @@
         <v>2024</v>
       </c>
       <c r="B252" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D252" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="E252" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="F252" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>96.58</v>
+        <v>96.53</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>16</v>
@@ -10565,25 +10556,25 @@
         <v>9</v>
       </c>
       <c r="C253" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F253" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D253" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G253" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>96.53</v>
+        <v>96.49</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>16</v>
@@ -10594,22 +10585,22 @@
         <v>2024</v>
       </c>
       <c r="B254" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C254" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G254" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10626,28 +10617,28 @@
         <v>2024</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="D255" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E255" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="E255" s="2" t="s">
-        <v>540</v>
-      </c>
       <c r="F255" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>96.49</v>
+        <v>96.44</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>16</v>
@@ -10658,22 +10649,22 @@
         <v>2024</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D256" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E256" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="E256" s="2" t="s">
-        <v>542</v>
-      </c>
       <c r="F256" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10690,28 +10681,28 @@
         <v>2024</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="D257" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E257" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="E257" s="2" t="s">
-        <v>544</v>
-      </c>
       <c r="F257" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>96.44</v>
+        <v>96.39</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>16</v>
@@ -10722,28 +10713,28 @@
         <v>2024</v>
       </c>
       <c r="B258" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D258" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="E258" s="2" t="s">
-        <v>546</v>
-      </c>
       <c r="F258" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>96.39</v>
+        <v>96.37</v>
       </c>
       <c r="J258" s="2" t="s">
         <v>16</v>
@@ -10754,28 +10745,28 @@
         <v>2024</v>
       </c>
       <c r="B259" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D259" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E259" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="E259" s="2" t="s">
-        <v>548</v>
-      </c>
       <c r="F259" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>96.37</v>
+        <v>96.34</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>16</v>
@@ -10786,28 +10777,28 @@
         <v>2024</v>
       </c>
       <c r="B260" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C260" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F260" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D260" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G260" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>96.34</v>
+        <v>96.33</v>
       </c>
       <c r="J260" s="2" t="s">
         <v>16</v>
@@ -10818,28 +10809,28 @@
         <v>2024</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D261" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E261" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="E261" s="2" t="s">
-        <v>552</v>
-      </c>
       <c r="F261" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>96.33</v>
+        <v>96.31</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>16</v>
@@ -10853,25 +10844,25 @@
         <v>9</v>
       </c>
       <c r="C262" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F262" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D262" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G262" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>96.31</v>
+        <v>96.29</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>16</v>
@@ -10882,28 +10873,28 @@
         <v>2024</v>
       </c>
       <c r="B263" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C263" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F263" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D263" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F263" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G263" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>96.29</v>
+        <v>96.28</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>16</v>
@@ -10914,28 +10905,28 @@
         <v>2024</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>496</v>
+        <v>556</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>96.28</v>
+        <v>96.26</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>16</v>
@@ -10946,28 +10937,28 @@
         <v>2024</v>
       </c>
       <c r="B265" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C265" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F265" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D265" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E265" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G265" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>96.26</v>
+        <v>96.22</v>
       </c>
       <c r="J265" s="2" t="s">
         <v>16</v>
@@ -10981,25 +10972,25 @@
         <v>10</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D266" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="E266" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="F266" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>96.22</v>
+        <v>96.2</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>16</v>
@@ -11010,28 +11001,28 @@
         <v>2024</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="D267" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="E267" s="2" t="s">
-        <v>563</v>
-      </c>
       <c r="F267" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>96.2</v>
+        <v>96.19</v>
       </c>
       <c r="J267" s="2" t="s">
         <v>16</v>
@@ -11045,19 +11036,19 @@
         <v>8</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D268" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E268" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="E268" s="2" t="s">
-        <v>565</v>
-      </c>
       <c r="F268" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11074,22 +11065,22 @@
         <v>2024</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D269" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E269" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="E269" s="2" t="s">
-        <v>567</v>
-      </c>
       <c r="F269" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11106,28 +11097,28 @@
         <v>2024</v>
       </c>
       <c r="B270" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D270" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E270" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="F270" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>96.19</v>
+        <v>96.18</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>16</v>
@@ -11141,25 +11132,25 @@
         <v>8</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D271" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E271" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E271" s="2" t="s">
-        <v>571</v>
-      </c>
       <c r="F271" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>96.18</v>
+        <v>96.15</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>16</v>
@@ -11173,25 +11164,25 @@
         <v>8</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D272" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E272" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E272" s="2" t="s">
-        <v>573</v>
-      </c>
       <c r="F272" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>96.15</v>
+        <v>96.14</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>16</v>
@@ -11205,25 +11196,25 @@
         <v>8</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D273" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E273" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="E273" s="2" t="s">
-        <v>575</v>
-      </c>
       <c r="F273" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>96.14</v>
+        <v>96.13</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>16</v>
@@ -11234,28 +11225,28 @@
         <v>2024</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D274" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E274" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="E274" s="2" t="s">
-        <v>577</v>
-      </c>
       <c r="F274" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>96.13</v>
+        <v>96.1</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>16</v>
@@ -11266,28 +11257,28 @@
         <v>2024</v>
       </c>
       <c r="B275" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C275" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D275" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G275" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>96.1</v>
+        <v>96.07</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>16</v>
@@ -11298,28 +11289,28 @@
         <v>2024</v>
       </c>
       <c r="B276" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D276" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E276" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="E276" s="2" t="s">
-        <v>581</v>
-      </c>
       <c r="F276" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>96.07</v>
+        <v>96.06</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>16</v>
@@ -11330,22 +11321,22 @@
         <v>2024</v>
       </c>
       <c r="B277" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D277" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="E277" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="E277" s="2" t="s">
-        <v>583</v>
-      </c>
       <c r="F277" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11362,28 +11353,28 @@
         <v>2024</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D278" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E278" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="E278" s="2" t="s">
-        <v>585</v>
-      </c>
       <c r="F278" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>96.06</v>
+        <v>96.05</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>16</v>
@@ -11394,28 +11385,28 @@
         <v>2024</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D279" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E279" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="E279" s="2" t="s">
-        <v>587</v>
-      </c>
       <c r="F279" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>96.05</v>
+        <v>96.04</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>16</v>
@@ -11426,28 +11417,28 @@
         <v>2024</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="D280" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E280" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="E280" s="2" t="s">
-        <v>589</v>
-      </c>
       <c r="F280" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>96.04</v>
+        <v>96.02</v>
       </c>
       <c r="J280" s="2" t="s">
         <v>16</v>
@@ -11458,28 +11449,28 @@
         <v>2024</v>
       </c>
       <c r="B281" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C281" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D281" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G281" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>96.02</v>
+        <v>96.01</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>16</v>
@@ -11490,22 +11481,22 @@
         <v>2024</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D282" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E282" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="E282" s="2" t="s">
-        <v>593</v>
-      </c>
       <c r="F282" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11522,28 +11513,28 @@
         <v>2024</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C283" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D283" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G283" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>96.01</v>
+        <v>96</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>16</v>
@@ -11557,25 +11548,25 @@
         <v>10</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D284" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E284" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="E284" s="2" t="s">
-        <v>597</v>
-      </c>
       <c r="F284" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>96</v>
+        <v>95.99</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>16</v>
@@ -11586,28 +11577,28 @@
         <v>2024</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D285" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E285" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="E285" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="F285" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>95.99</v>
+        <v>95.98</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>16</v>
@@ -11618,28 +11609,28 @@
         <v>2024</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C286" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D286" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G286" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>95.98</v>
+        <v>95.97</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>16</v>
@@ -11650,28 +11641,28 @@
         <v>2024</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D287" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E287" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="E287" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="F287" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>95.97</v>
+        <v>95.96</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>16</v>
@@ -11682,28 +11673,28 @@
         <v>2024</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="D288" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E288" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="E288" s="2" t="s">
-        <v>605</v>
-      </c>
       <c r="F288" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>95.96</v>
+        <v>95.94</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>16</v>
@@ -11714,28 +11705,28 @@
         <v>2024</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C289" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D289" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G289" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>95.94</v>
+        <v>95.88</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>16</v>
@@ -11746,22 +11737,22 @@
         <v>2024</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D290" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E290" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="E290" s="2" t="s">
-        <v>609</v>
-      </c>
       <c r="F290" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11781,25 +11772,25 @@
         <v>9</v>
       </c>
       <c r="C291" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F291" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D291" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G291" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>95.88</v>
+        <v>95.85</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>16</v>
@@ -11810,28 +11801,28 @@
         <v>2024</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C292" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="F292" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D292" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G292" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>95.85</v>
+        <v>95.83</v>
       </c>
       <c r="J292" s="2" t="s">
         <v>16</v>
@@ -11845,19 +11836,19 @@
         <v>10</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D293" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E293" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="E293" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="F293" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11874,28 +11865,28 @@
         <v>2024</v>
       </c>
       <c r="B294" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="D294" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E294" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="E294" s="2" t="s">
-        <v>617</v>
-      </c>
       <c r="F294" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>95.83</v>
+        <v>95.82</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>16</v>
@@ -11906,28 +11897,28 @@
         <v>2024</v>
       </c>
       <c r="B295" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D295" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E295" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="E295" s="2" t="s">
-        <v>619</v>
-      </c>
       <c r="F295" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>95.82</v>
+        <v>95.78</v>
       </c>
       <c r="J295" s="2" t="s">
         <v>16</v>
@@ -11941,25 +11932,25 @@
         <v>10</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D296" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E296" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="E296" s="2" t="s">
-        <v>621</v>
-      </c>
       <c r="F296" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>95.78</v>
+        <v>95.76</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>16</v>
@@ -11970,28 +11961,28 @@
         <v>2024</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D297" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E297" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="E297" s="2" t="s">
-        <v>623</v>
-      </c>
       <c r="F297" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>95.76</v>
+        <v>95.67</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>16</v>
@@ -12002,28 +11993,28 @@
         <v>2024</v>
       </c>
       <c r="B298" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C298" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="F298" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D298" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G298" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>95.67</v>
+        <v>95.66</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>16</v>
@@ -12037,25 +12028,25 @@
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D299" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="E299" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="E299" s="2" t="s">
-        <v>627</v>
-      </c>
       <c r="F299" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>95.66</v>
+        <v>95.62</v>
       </c>
       <c r="J299" s="2" t="s">
         <v>16</v>
@@ -12066,28 +12057,28 @@
         <v>2024</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D300" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E300" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="E300" s="2" t="s">
-        <v>629</v>
-      </c>
       <c r="F300" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>95.62</v>
+        <v>95.56</v>
       </c>
       <c r="J300" s="2" t="s">
         <v>16</v>
@@ -12098,22 +12089,22 @@
         <v>2024</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E301" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="F301" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D301" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G301" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12133,25 +12124,25 @@
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D302" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E302" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="E302" s="2" t="s">
-        <v>633</v>
-      </c>
       <c r="F302" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>95.56</v>
+        <v>95.47</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>16</v>
@@ -12165,25 +12156,25 @@
         <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D303" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E303" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="E303" s="2" t="s">
-        <v>635</v>
-      </c>
       <c r="F303" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>95.47</v>
+        <v>95.45</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>16</v>
@@ -12197,25 +12188,25 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D304" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E304" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="E304" s="2" t="s">
-        <v>637</v>
-      </c>
       <c r="F304" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>95.45</v>
+        <v>95.44</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>16</v>
@@ -12229,25 +12220,25 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D305" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E305" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="F305" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>95.44</v>
+        <v>95.43</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>16</v>
@@ -12258,28 +12249,28 @@
         <v>2024</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="D306" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E306" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E306" s="2" t="s">
-        <v>641</v>
-      </c>
       <c r="F306" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>95.43</v>
+        <v>95.39</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>16</v>
@@ -12290,28 +12281,28 @@
         <v>2024</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="D307" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E307" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="E307" s="2" t="s">
-        <v>643</v>
-      </c>
       <c r="F307" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>95.39</v>
+        <v>95.36</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>16</v>
@@ -12322,28 +12313,28 @@
         <v>2024</v>
       </c>
       <c r="B308" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C308" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="F308" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D308" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E308" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G308" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>95.36</v>
+        <v>95.29</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>16</v>
@@ -12357,25 +12348,25 @@
         <v>8</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D309" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E309" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="E309" s="2" t="s">
-        <v>647</v>
-      </c>
       <c r="F309" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>95.29</v>
+        <v>95.26</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>16</v>
@@ -12386,28 +12377,28 @@
         <v>2024</v>
       </c>
       <c r="B310" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D310" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E310" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="E310" s="2" t="s">
-        <v>649</v>
-      </c>
       <c r="F310" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>95.26</v>
+        <v>95.24</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>16</v>
@@ -12418,28 +12409,28 @@
         <v>2024</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D311" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E311" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="E311" s="2" t="s">
-        <v>651</v>
-      </c>
       <c r="F311" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>95.24</v>
+        <v>95.22</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>16</v>
@@ -12453,25 +12444,25 @@
         <v>8</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D312" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E312" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="E312" s="2" t="s">
-        <v>653</v>
-      </c>
       <c r="F312" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>95.22</v>
+        <v>94.95</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>16</v>
@@ -12485,25 +12476,25 @@
         <v>8</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D313" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="E313" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="E313" s="2" t="s">
-        <v>655</v>
-      </c>
       <c r="F313" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>94.95</v>
+        <v>94.94</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>16</v>
@@ -12514,28 +12505,28 @@
         <v>2024</v>
       </c>
       <c r="B314" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D314" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="E314" s="2" t="s">
-        <v>657</v>
-      </c>
       <c r="F314" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>94.94</v>
+        <v>94.87</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>16</v>
@@ -12546,28 +12537,28 @@
         <v>2024</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D315" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E315" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="E315" s="2" t="s">
-        <v>659</v>
-      </c>
       <c r="F315" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>94.87</v>
+        <v>94.63</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>16</v>
@@ -12581,25 +12572,25 @@
         <v>9</v>
       </c>
       <c r="C316" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="F316" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D316" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G316" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>94.63</v>
+        <v>94.62</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>16</v>
@@ -12610,28 +12601,28 @@
         <v>2024</v>
       </c>
       <c r="B317" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C317" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="F317" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D317" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G317" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>94.62</v>
+        <v>94.48</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>16</v>
@@ -12645,25 +12636,25 @@
         <v>10</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D318" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="E318" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="E318" s="2" t="s">
-        <v>665</v>
-      </c>
       <c r="F318" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>94.48</v>
+        <v>94.39</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>16</v>
@@ -12677,25 +12668,25 @@
         <v>10</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D319" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E319" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="E319" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="F319" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>94.39</v>
+        <v>93.88</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>16</v>
@@ -12706,28 +12697,28 @@
         <v>2024</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D320" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E320" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="E320" s="2" t="s">
-        <v>669</v>
-      </c>
       <c r="F320" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>93.88</v>
+        <v>93.84</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>16</v>
@@ -12738,28 +12729,28 @@
         <v>2024</v>
       </c>
       <c r="B321" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C321" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F321" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D321" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="E321" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="G321" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>93.84</v>
+        <v>93.54</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>16</v>
@@ -12770,28 +12761,28 @@
         <v>2024</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="D322" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E322" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E322" s="2" t="s">
-        <v>673</v>
-      </c>
       <c r="F322" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>93.54</v>
+        <v>93.41</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>16</v>
@@ -12802,28 +12793,28 @@
         <v>2024</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="D323" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E323" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="E323" s="2" t="s">
-        <v>675</v>
-      </c>
       <c r="F323" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>93.41</v>
+        <v>93.21</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>16</v>
@@ -12837,25 +12828,25 @@
         <v>10</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D324" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E324" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="E324" s="2" t="s">
-        <v>677</v>
-      </c>
       <c r="F324" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>93.21</v>
+        <v>92.41</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>16</v>
@@ -12866,67 +12857,35 @@
         <v>2024</v>
       </c>
       <c r="B325" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="D325" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="E325" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="E325" s="2" t="s">
-        <v>679</v>
-      </c>
       <c r="F325" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>92.41</v>
+        <v>89.54</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B326" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C326" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D326" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="E326" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G326" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="H326" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I326" s="2" t="n">
-        <v>89.54</v>
-      </c>
-      <c r="J326" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J326"/>
+  <autoFilter ref="A1:J325"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -12943,7 +12902,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -12951,50 +12910,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -13016,21 +12975,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13039,7 +12998,7 @@
         <v>2024</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_e_basneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_basneta_a_2024.xlsx
@@ -2062,7 +2062,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:54</t>
+    <t xml:space="preserve">2026-09-08 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
